--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122036405</v>
+        <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>74547</v>
+        <v>92053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519476</v>
+        <v>519795</v>
       </c>
       <c r="R2" t="n">
-        <v>6329172</v>
+        <v>6329046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122036406</v>
+        <v>122036405</v>
       </c>
       <c r="B3" t="n">
-        <v>92051</v>
+        <v>74549</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519795</v>
+        <v>519476</v>
       </c>
       <c r="R3" t="n">
-        <v>6329046</v>
+        <v>6329172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>92053</v>
+        <v>92054</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122036406</v>
+        <v>122036405</v>
       </c>
       <c r="B2" t="n">
-        <v>92054</v>
+        <v>74553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519795</v>
+        <v>519476</v>
       </c>
       <c r="R2" t="n">
-        <v>6329046</v>
+        <v>6329172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122036405</v>
+        <v>122036406</v>
       </c>
       <c r="B3" t="n">
-        <v>74549</v>
+        <v>92063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519476</v>
+        <v>519795</v>
       </c>
       <c r="R3" t="n">
-        <v>6329172</v>
+        <v>6329046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122036405</v>
+        <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>74553</v>
+        <v>92063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519476</v>
+        <v>519795</v>
       </c>
       <c r="R2" t="n">
-        <v>6329172</v>
+        <v>6329046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122036406</v>
+        <v>122036405</v>
       </c>
       <c r="B3" t="n">
-        <v>92063</v>
+        <v>74553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519795</v>
+        <v>519476</v>
       </c>
       <c r="R3" t="n">
-        <v>6329046</v>
+        <v>6329172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92070</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122036405</v>
       </c>
       <c r="B3" t="n">
-        <v>74553</v>
+        <v>74557</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>92070</v>
+        <v>92072</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122036405</v>
       </c>
       <c r="B3" t="n">
-        <v>74557</v>
+        <v>74559</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122036406</v>
+        <v>122036405</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>74559</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519795</v>
+        <v>519476</v>
       </c>
       <c r="R2" t="n">
-        <v>6329046</v>
+        <v>6329172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122036405</v>
+        <v>122036406</v>
       </c>
       <c r="B3" t="n">
-        <v>74559</v>
+        <v>92088</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519476</v>
+        <v>519795</v>
       </c>
       <c r="R3" t="n">
-        <v>6329172</v>
+        <v>6329046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122036406</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122036405</v>
+        <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>74559</v>
+        <v>92098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519476</v>
+        <v>519795</v>
       </c>
       <c r="R2" t="n">
-        <v>6329172</v>
+        <v>6329046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122036406</v>
+        <v>122036405</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>74559</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åker-Tvinnesheda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519795</v>
+        <v>519476</v>
       </c>
       <c r="R3" t="n">
-        <v>6329046</v>
+        <v>6329172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122036405</v>
       </c>
       <c r="B3" t="n">
-        <v>74559</v>
+        <v>74564</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12647-2020 artfynd.xlsx
+++ b/artfynd/A 12647-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122036406</v>
       </c>
       <c r="B2" t="n">
-        <v>92110</v>
+        <v>92115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
